--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46064</v>
+        <v>45727</v>
       </c>
       <c r="C1" s="1">
-        <v>46071</v>
+        <v>45734</v>
       </c>
       <c r="D1" s="1">
-        <v>46078</v>
+        <v>45741</v>
       </c>
       <c r="E1" s="1">
-        <v>46085</v>
+        <v>45748</v>
       </c>
       <c r="F1" s="1">
-        <v>46092</v>
+        <v>45755</v>
       </c>
       <c r="G1" s="1">
-        <v>46099</v>
+        <v>45762</v>
       </c>
       <c r="H1" s="1">
-        <v>46106</v>
+        <v>45769</v>
       </c>
       <c r="I1" s="1">
-        <v>46113</v>
+        <v>45776</v>
       </c>
       <c r="J1" s="1">
-        <v>46120</v>
+        <v>45783</v>
       </c>
       <c r="K1" s="1">
-        <v>46127</v>
+        <v>45790</v>
       </c>
       <c r="L1" s="1">
-        <v>46134</v>
+        <v>45797</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>26.9</v>
+        <v>36.8</v>
       </c>
       <c r="C2">
-        <v>26.9</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>35.5</v>
       </c>
       <c r="E2">
-        <v>27.1</v>
+        <v>35.5</v>
       </c>
       <c r="F2">
-        <v>27.1</v>
+        <v>35.9</v>
       </c>
       <c r="G2">
-        <v>27.2</v>
+        <v>36.7</v>
       </c>
       <c r="H2">
-        <v>27.2</v>
+        <v>37.8</v>
       </c>
       <c r="I2">
-        <v>27.2</v>
+        <v>39.1</v>
       </c>
       <c r="J2">
-        <v>27.2</v>
+        <v>40.5</v>
       </c>
       <c r="K2">
-        <v>27.2</v>
+        <v>41.9</v>
       </c>
       <c r="L2">
-        <v>27.4</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
       <c r="C3">
+        <v>30.9</v>
+      </c>
+      <c r="D3">
+        <v>30.7</v>
+      </c>
+      <c r="E3">
         <v>30.8</v>
       </c>
-      <c r="D3">
-        <v>31.2</v>
-      </c>
-      <c r="E3">
-        <v>31.3</v>
-      </c>
       <c r="F3">
-        <v>30.9</v>
+        <v>31.4</v>
       </c>
       <c r="G3">
-        <v>30.2</v>
+        <v>32.2</v>
       </c>
       <c r="H3">
-        <v>29.2</v>
+        <v>33.2</v>
       </c>
       <c r="I3">
-        <v>28</v>
+        <v>34.4</v>
       </c>
       <c r="J3">
-        <v>26.7</v>
+        <v>35.6</v>
       </c>
       <c r="K3">
-        <v>25.5</v>
+        <v>36.8</v>
       </c>
       <c r="L3">
-        <v>24.5</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>29.4</v>
       </c>
       <c r="C4">
-        <v>28.5</v>
+        <v>28.3</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="E4">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="F4">
-        <v>27.1</v>
+        <v>27.9</v>
       </c>
       <c r="G4">
-        <v>26.9</v>
+        <v>28.7</v>
       </c>
       <c r="H4">
-        <v>26.8</v>
+        <v>29.7</v>
       </c>
       <c r="I4">
-        <v>27</v>
+        <v>30.8</v>
       </c>
       <c r="J4">
-        <v>27.4</v>
+        <v>32.1</v>
       </c>
       <c r="K4">
-        <v>28</v>
+        <v>33.3</v>
       </c>
       <c r="L4">
-        <v>28.8</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>39.2</v>
+        <v>50.2</v>
       </c>
       <c r="C5">
-        <v>39.3</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>38.9</v>
+        <v>42.2</v>
       </c>
       <c r="E5">
+        <v>39.1</v>
+      </c>
+      <c r="F5">
+        <v>37</v>
+      </c>
+      <c r="G5">
+        <v>35.9</v>
+      </c>
+      <c r="H5">
+        <v>35.7</v>
+      </c>
+      <c r="I5">
+        <v>36.4</v>
+      </c>
+      <c r="J5">
         <v>37.8</v>
       </c>
-      <c r="F5">
-        <v>35.8</v>
-      </c>
-      <c r="G5">
-        <v>33</v>
-      </c>
-      <c r="H5">
-        <v>29.4</v>
-      </c>
-      <c r="I5">
-        <v>25.3</v>
-      </c>
-      <c r="J5">
-        <v>20.9</v>
-      </c>
       <c r="K5">
-        <v>16.7</v>
+        <v>39.6</v>
       </c>
       <c r="L5">
-        <v>13</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>24.7</v>
+        <v>39.5</v>
       </c>
       <c r="C6">
-        <v>24.3</v>
+        <v>39.6</v>
       </c>
       <c r="D6">
-        <v>24.2</v>
+        <v>39.9</v>
       </c>
       <c r="E6">
-        <v>24.2</v>
+        <v>40.5</v>
       </c>
       <c r="F6">
-        <v>24.2</v>
+        <v>41.4</v>
       </c>
       <c r="G6">
-        <v>24.2</v>
+        <v>42.6</v>
       </c>
       <c r="H6">
-        <v>24.3</v>
+        <v>44.1</v>
       </c>
       <c r="I6">
-        <v>24.3</v>
+        <v>45.8</v>
       </c>
       <c r="J6">
-        <v>24.4</v>
+        <v>47.5</v>
       </c>
       <c r="K6">
-        <v>24.6</v>
+        <v>49.1</v>
       </c>
       <c r="L6">
-        <v>24.9</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>21.7</v>
+        <v>29.4</v>
       </c>
       <c r="C7">
-        <v>21.4</v>
+        <v>28.8</v>
       </c>
       <c r="D7">
-        <v>21.4</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>21.7</v>
+        <v>29.8</v>
       </c>
       <c r="F7">
-        <v>22.2</v>
+        <v>31.2</v>
       </c>
       <c r="G7">
-        <v>23.1</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>24.2</v>
+        <v>34.8</v>
       </c>
       <c r="I7">
-        <v>25.5</v>
+        <v>36.7</v>
       </c>
       <c r="J7">
-        <v>27</v>
+        <v>38.5</v>
       </c>
       <c r="K7">
-        <v>28.6</v>
+        <v>40.2</v>
       </c>
       <c r="L7">
-        <v>30.2</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>19.6</v>
+        <v>25.6</v>
       </c>
       <c r="C8">
-        <v>19</v>
+        <v>25.9</v>
       </c>
       <c r="D8">
-        <v>18.8</v>
+        <v>26.8</v>
       </c>
       <c r="E8">
-        <v>19</v>
+        <v>28.2</v>
       </c>
       <c r="F8">
-        <v>19.7</v>
+        <v>30.2</v>
       </c>
       <c r="G8">
-        <v>20.9</v>
+        <v>32.3</v>
       </c>
       <c r="H8">
-        <v>22.5</v>
+        <v>34.4</v>
       </c>
       <c r="I8">
-        <v>24.5</v>
+        <v>36.5</v>
       </c>
       <c r="J8">
-        <v>26.7</v>
+        <v>38.3</v>
       </c>
       <c r="K8">
-        <v>29</v>
+        <v>39.8</v>
       </c>
       <c r="L8">
-        <v>31.3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>16.6</v>
+        <v>33.5</v>
       </c>
       <c r="C9">
-        <v>17.4</v>
+        <v>34</v>
       </c>
       <c r="D9">
-        <v>18.8</v>
+        <v>34.7</v>
       </c>
       <c r="E9">
-        <v>20.7</v>
+        <v>35.7</v>
       </c>
       <c r="F9">
-        <v>23.2</v>
+        <v>37</v>
       </c>
       <c r="G9">
-        <v>26.1</v>
+        <v>38.4</v>
       </c>
       <c r="H9">
-        <v>29.2</v>
+        <v>39.7</v>
       </c>
       <c r="I9">
-        <v>32.6</v>
+        <v>40.7</v>
       </c>
       <c r="J9">
-        <v>35.9</v>
+        <v>41.3</v>
       </c>
       <c r="K9">
-        <v>39.1</v>
+        <v>41.6</v>
       </c>
       <c r="L9">
-        <v>42</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>31.9</v>
+        <v>47</v>
       </c>
       <c r="C10">
-        <v>32.4</v>
+        <v>46.8</v>
       </c>
       <c r="D10">
-        <v>33.1</v>
+        <v>46.9</v>
       </c>
       <c r="E10">
-        <v>33.6</v>
+        <v>47.3</v>
       </c>
       <c r="F10">
-        <v>33.8</v>
+        <v>48.1</v>
       </c>
       <c r="G10">
-        <v>33.7</v>
+        <v>49.3</v>
       </c>
       <c r="H10">
-        <v>33.3</v>
+        <v>51</v>
       </c>
       <c r="I10">
-        <v>32.6</v>
+        <v>52.8</v>
       </c>
       <c r="J10">
-        <v>31.7</v>
+        <v>54.8</v>
       </c>
       <c r="K10">
-        <v>30.7</v>
+        <v>56.6</v>
       </c>
       <c r="L10">
-        <v>29.9</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>44.6</v>
       </c>
       <c r="C11">
-        <v>17.9</v>
+        <v>44.5</v>
       </c>
       <c r="D11">
-        <v>18.1</v>
+        <v>44.3</v>
       </c>
       <c r="E11">
-        <v>18.7</v>
+        <v>44.2</v>
       </c>
       <c r="F11">
-        <v>19.5</v>
+        <v>44.5</v>
       </c>
       <c r="G11">
-        <v>20.5</v>
+        <v>45.2</v>
       </c>
       <c r="H11">
-        <v>21.7</v>
+        <v>46.2</v>
       </c>
       <c r="I11">
-        <v>23.1</v>
+        <v>47.4</v>
       </c>
       <c r="J11">
-        <v>24.5</v>
+        <v>48.7</v>
       </c>
       <c r="K11">
-        <v>26.1</v>
+        <v>50</v>
       </c>
       <c r="L11">
-        <v>27.7</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="C12">
-        <v>37.6</v>
+        <v>35.2</v>
       </c>
       <c r="D12">
-        <v>37.1</v>
+        <v>33.1</v>
       </c>
       <c r="E12">
-        <v>36.3</v>
+        <v>31.4</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>30.3</v>
       </c>
       <c r="G12">
-        <v>33.3</v>
+        <v>29.7</v>
       </c>
       <c r="H12">
-        <v>31.3</v>
+        <v>29.6</v>
       </c>
       <c r="I12">
-        <v>28.9</v>
+        <v>29.9</v>
       </c>
       <c r="J12">
-        <v>26.5</v>
+        <v>30.7</v>
       </c>
       <c r="K12">
-        <v>24.1</v>
+        <v>31.7</v>
       </c>
       <c r="L12">
-        <v>22.1</v>
+        <v>32.9</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>45727</v>
+        <v>46078</v>
       </c>
       <c r="C1" s="1">
-        <v>45734</v>
+        <v>46085</v>
       </c>
       <c r="D1" s="1">
-        <v>45741</v>
+        <v>46092</v>
       </c>
       <c r="E1" s="1">
-        <v>45748</v>
+        <v>46099</v>
       </c>
       <c r="F1" s="1">
-        <v>45755</v>
+        <v>46106</v>
       </c>
       <c r="G1" s="1">
-        <v>45762</v>
+        <v>46113</v>
       </c>
       <c r="H1" s="1">
-        <v>45769</v>
+        <v>46120</v>
       </c>
       <c r="I1" s="1">
-        <v>45776</v>
+        <v>46127</v>
       </c>
       <c r="J1" s="1">
-        <v>45783</v>
+        <v>46134</v>
       </c>
       <c r="K1" s="1">
-        <v>45790</v>
+        <v>46141</v>
       </c>
       <c r="L1" s="1">
-        <v>45797</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>36.8</v>
+        <v>27.2</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>27.5</v>
       </c>
       <c r="D2">
-        <v>35.5</v>
+        <v>27.9</v>
       </c>
       <c r="E2">
-        <v>35.5</v>
+        <v>28.3</v>
       </c>
       <c r="F2">
-        <v>35.9</v>
+        <v>28.7</v>
       </c>
       <c r="G2">
-        <v>36.7</v>
+        <v>29.1</v>
       </c>
       <c r="H2">
-        <v>37.8</v>
+        <v>29.7</v>
       </c>
       <c r="I2">
-        <v>39.1</v>
+        <v>30.2</v>
       </c>
       <c r="J2">
-        <v>40.5</v>
+        <v>30.9</v>
       </c>
       <c r="K2">
-        <v>41.9</v>
+        <v>31.7</v>
       </c>
       <c r="L2">
-        <v>43.1</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
+        <v>31.7</v>
+      </c>
+      <c r="C3">
+        <v>32.1</v>
+      </c>
+      <c r="D3">
+        <v>32.3</v>
+      </c>
+      <c r="E3">
+        <v>32.3</v>
+      </c>
+      <c r="F3">
+        <v>32.1</v>
+      </c>
+      <c r="G3">
+        <v>31.8</v>
+      </c>
+      <c r="H3">
         <v>31.4</v>
       </c>
-      <c r="C3">
-        <v>30.9</v>
-      </c>
-      <c r="D3">
-        <v>30.7</v>
-      </c>
-      <c r="E3">
-        <v>30.8</v>
-      </c>
-      <c r="F3">
-        <v>31.4</v>
-      </c>
-      <c r="G3">
-        <v>32.2</v>
-      </c>
-      <c r="H3">
-        <v>33.2</v>
-      </c>
       <c r="I3">
-        <v>34.4</v>
+        <v>31.2</v>
       </c>
       <c r="J3">
-        <v>35.6</v>
+        <v>31.1</v>
       </c>
       <c r="K3">
-        <v>36.8</v>
+        <v>31.2</v>
       </c>
       <c r="L3">
-        <v>37.8</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>29.4</v>
+        <v>27.9</v>
       </c>
       <c r="C4">
-        <v>28.3</v>
+        <v>27.3</v>
       </c>
       <c r="D4">
-        <v>27.7</v>
+        <v>26.6</v>
       </c>
       <c r="E4">
-        <v>27.6</v>
+        <v>26</v>
       </c>
       <c r="F4">
-        <v>27.9</v>
+        <v>25.6</v>
       </c>
       <c r="G4">
-        <v>28.7</v>
+        <v>25.2</v>
       </c>
       <c r="H4">
-        <v>29.7</v>
+        <v>25.1</v>
       </c>
       <c r="I4">
-        <v>30.8</v>
+        <v>25.1</v>
       </c>
       <c r="J4">
-        <v>32.1</v>
+        <v>25.3</v>
       </c>
       <c r="K4">
-        <v>33.3</v>
+        <v>25.7</v>
       </c>
       <c r="L4">
-        <v>34.5</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>50.2</v>
+        <v>40.2</v>
       </c>
       <c r="C5">
-        <v>46</v>
+        <v>40.4</v>
       </c>
       <c r="D5">
-        <v>42.2</v>
+        <v>40.2</v>
       </c>
       <c r="E5">
-        <v>39.1</v>
+        <v>39.6</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>38.7</v>
       </c>
       <c r="G5">
-        <v>35.9</v>
+        <v>37.5</v>
       </c>
       <c r="H5">
+        <v>36.4</v>
+      </c>
+      <c r="I5">
+        <v>35.4</v>
+      </c>
+      <c r="J5">
+        <v>34.9</v>
+      </c>
+      <c r="K5">
+        <v>35</v>
+      </c>
+      <c r="L5">
         <v>35.7</v>
-      </c>
-      <c r="I5">
-        <v>36.4</v>
-      </c>
-      <c r="J5">
-        <v>37.8</v>
-      </c>
-      <c r="K5">
-        <v>39.6</v>
-      </c>
-      <c r="L5">
-        <v>41.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>39.5</v>
+        <v>24.8</v>
       </c>
       <c r="C6">
-        <v>39.6</v>
+        <v>25.4</v>
       </c>
       <c r="D6">
-        <v>39.9</v>
+        <v>26.2</v>
       </c>
       <c r="E6">
-        <v>40.5</v>
+        <v>27.2</v>
       </c>
       <c r="F6">
-        <v>41.4</v>
+        <v>28.4</v>
       </c>
       <c r="G6">
-        <v>42.6</v>
+        <v>29.8</v>
       </c>
       <c r="H6">
-        <v>44.1</v>
+        <v>31.4</v>
       </c>
       <c r="I6">
-        <v>45.8</v>
+        <v>33.2</v>
       </c>
       <c r="J6">
-        <v>47.5</v>
+        <v>35</v>
       </c>
       <c r="K6">
-        <v>49.1</v>
+        <v>36.8</v>
       </c>
       <c r="L6">
-        <v>50.4</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>29.4</v>
+        <v>21.2</v>
       </c>
       <c r="C7">
-        <v>28.8</v>
+        <v>21.2</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>21.3</v>
       </c>
       <c r="E7">
-        <v>29.8</v>
+        <v>21.7</v>
       </c>
       <c r="F7">
-        <v>31.2</v>
+        <v>22.2</v>
       </c>
       <c r="G7">
-        <v>33</v>
+        <v>22.9</v>
       </c>
       <c r="H7">
-        <v>34.8</v>
+        <v>23.7</v>
       </c>
       <c r="I7">
-        <v>36.7</v>
+        <v>24.5</v>
       </c>
       <c r="J7">
-        <v>38.5</v>
+        <v>25.4</v>
       </c>
       <c r="K7">
-        <v>40.2</v>
+        <v>26.4</v>
       </c>
       <c r="L7">
-        <v>41.7</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>25.6</v>
+        <v>18.4</v>
       </c>
       <c r="C8">
+        <v>18.2</v>
+      </c>
+      <c r="D8">
+        <v>18.3</v>
+      </c>
+      <c r="E8">
+        <v>18.8</v>
+      </c>
+      <c r="F8">
+        <v>19.6</v>
+      </c>
+      <c r="G8">
+        <v>20.5</v>
+      </c>
+      <c r="H8">
+        <v>21.6</v>
+      </c>
+      <c r="I8">
+        <v>22.8</v>
+      </c>
+      <c r="J8">
+        <v>23.9</v>
+      </c>
+      <c r="K8">
+        <v>24.9</v>
+      </c>
+      <c r="L8">
         <v>25.9</v>
-      </c>
-      <c r="D8">
-        <v>26.8</v>
-      </c>
-      <c r="E8">
-        <v>28.2</v>
-      </c>
-      <c r="F8">
-        <v>30.2</v>
-      </c>
-      <c r="G8">
-        <v>32.3</v>
-      </c>
-      <c r="H8">
-        <v>34.4</v>
-      </c>
-      <c r="I8">
-        <v>36.5</v>
-      </c>
-      <c r="J8">
-        <v>38.3</v>
-      </c>
-      <c r="K8">
-        <v>39.8</v>
-      </c>
-      <c r="L8">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>33.5</v>
+        <v>18.2</v>
       </c>
       <c r="C9">
-        <v>34</v>
+        <v>19.4</v>
       </c>
       <c r="D9">
-        <v>34.7</v>
+        <v>20.8</v>
       </c>
       <c r="E9">
-        <v>35.7</v>
+        <v>22.4</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G9">
-        <v>38.4</v>
+        <v>25.6</v>
       </c>
       <c r="H9">
-        <v>39.7</v>
+        <v>27</v>
       </c>
       <c r="I9">
-        <v>40.7</v>
+        <v>28.2</v>
       </c>
       <c r="J9">
-        <v>41.3</v>
+        <v>29.1</v>
       </c>
       <c r="K9">
-        <v>41.6</v>
+        <v>29.8</v>
       </c>
       <c r="L9">
-        <v>41.4</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>47</v>
+        <v>33.8</v>
       </c>
       <c r="C10">
-        <v>46.8</v>
+        <v>35.1</v>
       </c>
       <c r="D10">
-        <v>46.9</v>
+        <v>36.3</v>
       </c>
       <c r="E10">
-        <v>47.3</v>
+        <v>37.5</v>
       </c>
       <c r="F10">
-        <v>48.1</v>
+        <v>38.7</v>
       </c>
       <c r="G10">
-        <v>49.3</v>
+        <v>39.7</v>
       </c>
       <c r="H10">
-        <v>51</v>
+        <v>40.7</v>
       </c>
       <c r="I10">
-        <v>52.8</v>
+        <v>41.7</v>
       </c>
       <c r="J10">
-        <v>54.8</v>
+        <v>42.7</v>
       </c>
       <c r="K10">
-        <v>56.6</v>
+        <v>43.7</v>
       </c>
       <c r="L10">
-        <v>58.2</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>44.6</v>
+        <v>18.4</v>
       </c>
       <c r="C11">
-        <v>44.5</v>
+        <v>19.2</v>
       </c>
       <c r="D11">
-        <v>44.3</v>
+        <v>20.4</v>
       </c>
       <c r="E11">
-        <v>44.2</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>44.5</v>
+        <v>23.9</v>
       </c>
       <c r="G11">
-        <v>45.2</v>
+        <v>26</v>
       </c>
       <c r="H11">
-        <v>46.2</v>
+        <v>28.4</v>
       </c>
       <c r="I11">
-        <v>47.4</v>
+        <v>30.9</v>
       </c>
       <c r="J11">
-        <v>48.7</v>
+        <v>33.4</v>
       </c>
       <c r="K11">
-        <v>50</v>
+        <v>35.9</v>
       </c>
       <c r="L11">
-        <v>51</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="C12">
-        <v>35.2</v>
+        <v>37.1</v>
       </c>
       <c r="D12">
-        <v>33.1</v>
+        <v>36.3</v>
       </c>
       <c r="E12">
-        <v>31.4</v>
+        <v>35.3</v>
       </c>
       <c r="F12">
-        <v>30.3</v>
+        <v>33.9</v>
       </c>
       <c r="G12">
-        <v>29.7</v>
+        <v>32.4</v>
       </c>
       <c r="H12">
-        <v>29.6</v>
+        <v>30.9</v>
       </c>
       <c r="I12">
-        <v>29.9</v>
+        <v>29.4</v>
       </c>
       <c r="J12">
-        <v>30.7</v>
+        <v>28.2</v>
       </c>
       <c r="K12">
-        <v>31.7</v>
+        <v>27.4</v>
       </c>
       <c r="L12">
-        <v>32.9</v>
+        <v>27.1</v>
       </c>
     </row>
   </sheetData>
